--- a/www/terminologies/CodeSystem-terminologie-nuva.xlsx
+++ b/www/terminologies/CodeSystem-terminologie-nuva.xlsx
@@ -40,7 +40,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.0.1042</t>
+    <t>1.0.1052</t>
   </si>
   <si>
     <t>Name</t>
@@ -70,7 +70,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-11-26T00:00:00+00:00</t>
+    <t>2025-12-18T00:00:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -130,7 +130,7 @@
     <t>Count</t>
   </si>
   <si>
-    <t>1899</t>
+    <t>1906</t>
   </si>
   <si>
     <t>Code</t>

--- a/www/terminologies/CodeSystem-terminologie-nuva.xlsx
+++ b/www/terminologies/CodeSystem-terminologie-nuva.xlsx
@@ -40,7 +40,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.0.1052</t>
+    <t>1.0.1063</t>
   </si>
   <si>
     <t>Name</t>
@@ -70,7 +70,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-12-18T00:00:00+00:00</t>
+    <t>2026-01-29T00:00:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -130,7 +130,7 @@
     <t>Count</t>
   </si>
   <si>
-    <t>1906</t>
+    <t>1927</t>
   </si>
   <si>
     <t>Code</t>

--- a/www/terminologies/CodeSystem-terminologie-nuva.xlsx
+++ b/www/terminologies/CodeSystem-terminologie-nuva.xlsx
@@ -40,7 +40,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.0.1063</t>
+    <t>1.0.1072</t>
   </si>
   <si>
     <t>Name</t>
@@ -70,7 +70,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-29T00:00:00+00:00</t>
+    <t>2026-03-01T00:00:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/www/terminologies/CodeSystem-terminologie-nuva.xlsx
+++ b/www/terminologies/CodeSystem-terminologie-nuva.xlsx
@@ -40,7 +40,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.0.1072</t>
+    <t>1.0.1078</t>
   </si>
   <si>
     <t>Name</t>
@@ -70,7 +70,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-01T00:00:00+00:00</t>
+    <t>2026-03-24T00:00:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -130,7 +130,7 @@
     <t>Count</t>
   </si>
   <si>
-    <t>1927</t>
+    <t>1942</t>
   </si>
   <si>
     <t>Code</t>
@@ -160,12 +160,36 @@
     <t>dateTime</t>
   </si>
   <si>
+    <t>comment</t>
+  </si>
+  <si>
+    <t>http://www.w3.org/2000/01/rdf-schema#comment</t>
+  </si>
+  <si>
+    <t>string</t>
+  </si>
+  <si>
     <t>modified</t>
   </si>
   <si>
     <t>http://purl.org/dc/terms/modified</t>
   </si>
   <si>
+    <t>containsValence</t>
+  </si>
+  <si>
+    <t>http://data.esante.gouv.fr/NUVA/nuvs#containsValence</t>
+  </si>
+  <si>
+    <t>isAbstract</t>
+  </si>
+  <si>
+    <t>http://data.esante.gouv.fr/NUVA/nuvs#isAbstract</t>
+  </si>
+  <si>
+    <t>boolean</t>
+  </si>
+  <si>
     <t>containedInVaccine</t>
   </si>
   <si>
@@ -176,30 +200,6 @@
   </si>
   <si>
     <t>http://data.esante.gouv.fr/NUVA/nuvs#prevents</t>
-  </si>
-  <si>
-    <t>comment</t>
-  </si>
-  <si>
-    <t>http://www.w3.org/2000/01/rdf-schema#comment</t>
-  </si>
-  <si>
-    <t>string</t>
-  </si>
-  <si>
-    <t>containsValence</t>
-  </si>
-  <si>
-    <t>http://data.esante.gouv.fr/NUVA/nuvs#containsValence</t>
-  </si>
-  <si>
-    <t>isAbstract</t>
-  </si>
-  <si>
-    <t>http://data.esante.gouv.fr/NUVA/nuvs#isAbstract</t>
-  </si>
-  <si>
-    <t>boolean</t>
   </si>
   <si>
     <t>hiddenLabel</t>
@@ -620,27 +620,27 @@
       </c>
       <c r="C4" s="2"/>
       <c r="D4" t="s" s="2">
-        <v>47</v>
+        <v>50</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" t="s" s="2">
-        <v>44</v>
+        <v>47</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
@@ -649,22 +649,22 @@
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
@@ -673,14 +673,14 @@
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
-        <v>61</v>
+        <v>44</v>
       </c>
     </row>
     <row r="10">
@@ -692,7 +692,7 @@
       </c>
       <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
-        <v>56</v>
+        <v>50</v>
       </c>
     </row>
     <row r="11">
@@ -732,7 +732,7 @@
         <v>71</v>
       </c>
       <c r="D13" t="s" s="2">
-        <v>61</v>
+        <v>57</v>
       </c>
     </row>
     <row r="14">
@@ -744,7 +744,7 @@
         <v>73</v>
       </c>
       <c r="D14" t="s" s="2">
-        <v>61</v>
+        <v>57</v>
       </c>
     </row>
   </sheetData>

--- a/www/terminologies/CodeSystem-terminologie-nuva.xlsx
+++ b/www/terminologies/CodeSystem-terminologie-nuva.xlsx
@@ -40,7 +40,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.0.1078</t>
+    <t>1.0.1096</t>
   </si>
   <si>
     <t>Name</t>
@@ -70,7 +70,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-24T00:00:00+00:00</t>
+    <t>2026-05-06T00:00:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/www/terminologies/CodeSystem-terminologie-nuva.xlsx
+++ b/www/terminologies/CodeSystem-terminologie-nuva.xlsx
@@ -40,7 +40,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.0.1096</t>
+    <t>1.0.1108</t>
   </si>
   <si>
     <t>Name</t>
@@ -70,7 +70,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-06T00:00:00+00:00</t>
+    <t>2026-05-27T00:00:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/www/terminologies/CodeSystem-terminologie-nuva.xlsx
+++ b/www/terminologies/CodeSystem-terminologie-nuva.xlsx
@@ -40,7 +40,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.0.1108</t>
+    <t>1.0.1096</t>
   </si>
   <si>
     <t>Name</t>
@@ -70,7 +70,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-27T00:00:00+00:00</t>
+    <t>2026-05-06T00:00:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/www/terminologies/CodeSystem-terminologie-nuva.xlsx
+++ b/www/terminologies/CodeSystem-terminologie-nuva.xlsx
@@ -40,7 +40,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.0.1108</t>
+    <t>1.0.1110</t>
   </si>
   <si>
     <t>Name</t>
@@ -70,7 +70,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-27T00:00:00+00:00</t>
+    <t>2026-06-05T00:00:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
